--- a/artfynd/A 23157-2024 artfynd.xlsx
+++ b/artfynd/A 23157-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117766306</v>
       </c>
       <c r="B2" t="n">
-        <v>95131</v>
+        <v>95133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23157-2024 artfynd.xlsx
+++ b/artfynd/A 23157-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>118676068</v>
       </c>
       <c r="B3" t="n">
-        <v>95141</v>
+        <v>95148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
